--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-sequencingExperimentExtension.xlsx
+++ b/docs/StructureDefinition-sequencingExperimentExtension.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="220">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -289,7 +289,7 @@
     <t>Extension.extension</t>
   </si>
   <si>
-    <t>6</t>
+    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -318,6 +318,9 @@
     <t>experimentalStrategy</t>
   </si>
   <si>
+    <t>Experimental strategy of the experiment.</t>
+  </si>
+  <si>
     <t>Extension.extension:experimentalStrategy.id</t>
   </si>
   <si>
@@ -384,13 +387,37 @@
 </t>
   </si>
   <si>
+    <t>Extension.extension:profilingResolution</t>
+  </si>
+  <si>
+    <t>profilingResolution</t>
+  </si>
+  <si>
+    <t>Resolution at which the sample is profiled.</t>
+  </si>
+  <si>
+    <t>Extension.extension:profilingResolution.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:profilingResolution.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:profilingResolution.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:profilingResolution.value[x]</t>
+  </si>
+  <si>
+    <t>https://fhir.cqdg.ca/ValueSet/profiling-resolution-vs</t>
+  </si>
+  <si>
     <t>Extension.extension:isPairedEnd</t>
   </si>
   <si>
     <t>isPairedEnd</t>
   </si>
   <si>
-    <t>No description</t>
+    <t>Whether the run is paired-end.</t>
   </si>
   <si>
     <t>Extension.extension:isPairedEnd.id</t>
@@ -415,6 +442,9 @@
     <t>platform</t>
   </si>
   <si>
+    <t>Platform used for the experiment.</t>
+  </si>
+  <si>
     <t>Extension.extension:platform.id</t>
   </si>
   <si>
@@ -430,12 +460,57 @@
     <t>https://fhir.cqdg.ca/ValueSet/sequencing-experiment-platform-vs</t>
   </si>
   <si>
+    <t>Extension.extension:instrumentModel</t>
+  </si>
+  <si>
+    <t>instrumentModel</t>
+  </si>
+  <si>
+    <t>Instrument model.</t>
+  </si>
+  <si>
+    <t>Extension.extension:instrumentModel.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:instrumentModel.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:instrumentModel.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:instrumentModel.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:poreType</t>
+  </si>
+  <si>
+    <t>poreType</t>
+  </si>
+  <si>
+    <t>ONT pore chemistry.</t>
+  </si>
+  <si>
+    <t>Extension.extension:poreType.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:poreType.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:poreType.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:poreType.value[x]</t>
+  </si>
+  <si>
     <t>Extension.extension:protocol</t>
   </si>
   <si>
     <t>protocol</t>
   </si>
   <si>
+    <t>No description</t>
+  </si>
+  <si>
     <t>Extension.extension:protocol.id</t>
   </si>
   <si>
@@ -496,6 +571,9 @@
     <t>source</t>
   </si>
   <si>
+    <t>Experimental category of the experiment.</t>
+  </si>
+  <si>
     <t>Extension.extension:source.id</t>
   </si>
   <si>
@@ -509,6 +587,27 @@
   </si>
   <si>
     <t>https://fhir.cqdg.ca/ValueSet/sequencing-experiment-source-vs</t>
+  </si>
+  <si>
+    <t>Extension.extension:isImputed</t>
+  </si>
+  <si>
+    <t>isImputed</t>
+  </si>
+  <si>
+    <t>Whether the variant calls were imputed.</t>
+  </si>
+  <si>
+    <t>Extension.extension:isImputed.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:isImputed.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:isImputed.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:isImputed.value[x]</t>
   </si>
   <si>
     <t>Extension.extension:targetCaptureKit</t>
@@ -913,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="true" bestFit="true"/>
@@ -1394,7 +1493,7 @@
         <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1412,7 +1511,7 @@
         <v>30</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1483,10 +1582,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1586,10 +1685,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1689,10 +1788,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1715,16 +1814,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1774,7 +1873,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>82</v>
@@ -1789,15 +1888,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1820,13 +1919,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1853,11 +1952,11 @@
         <v>20</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>20</v>
@@ -1875,7 +1974,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1887,31 +1986,31 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1929,7 +2028,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2000,10 +2099,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2103,10 +2202,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2206,10 +2305,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2232,16 +2331,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2249,7 +2348,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2291,7 +2390,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -2306,15 +2405,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2337,13 +2436,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2370,13 +2469,11 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2394,7 +2491,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2406,28 +2503,28 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -2448,7 +2545,7 @@
         <v>30</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2519,10 +2616,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2622,10 +2719,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2725,10 +2822,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2751,16 +2848,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2768,7 +2865,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>20</v>
@@ -2810,7 +2907,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -2825,15 +2922,15 @@
         <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2856,13 +2953,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2889,11 +2986,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -2911,7 +3010,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -2923,31 +3022,31 @@
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2965,7 +3064,7 @@
         <v>30</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3036,10 +3135,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3139,10 +3238,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3242,10 +3341,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3268,16 +3367,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3285,7 +3384,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>20</v>
@@ -3327,7 +3426,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -3342,15 +3441,15 @@
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3373,13 +3472,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3406,13 +3505,11 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -3430,7 +3527,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3442,31 +3539,31 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3484,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3555,10 +3652,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3658,10 +3755,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3761,10 +3858,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3787,16 +3884,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3804,7 +3901,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>20</v>
@@ -3846,7 +3943,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -3861,15 +3958,15 @@
         <v>20</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3895,10 +3992,10 @@
         <v>83</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3949,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -3961,34 +4058,34 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4003,7 +4100,7 @@
         <v>30</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4074,10 +4171,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4177,10 +4274,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4280,10 +4377,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4306,16 +4403,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4323,7 +4420,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>20</v>
@@ -4365,7 +4462,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -4380,15 +4477,15 @@
         <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4411,13 +4508,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4444,11 +4541,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -4466,7 +4565,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4478,34 +4577,34 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -4520,7 +4619,7 @@
         <v>30</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4591,10 +4690,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4694,10 +4793,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4797,10 +4896,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4823,16 +4922,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4840,7 +4939,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>20</v>
@@ -4882,7 +4981,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -4897,15 +4996,15 @@
         <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4928,13 +5027,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4961,11 +5060,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -4983,7 +5084,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -4995,21 +5096,21 @@
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
@@ -5037,7 +5138,7 @@
         <v>30</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5108,10 +5209,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5211,10 +5312,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5314,10 +5415,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5340,16 +5441,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5357,7 +5458,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>20</v>
@@ -5399,7 +5500,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -5414,15 +5515,15 @@
         <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5448,10 +5549,10 @@
         <v>83</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5502,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5514,34 +5615,34 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -5556,7 +5657,7 @@
         <v>30</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5627,10 +5728,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5730,10 +5831,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5833,10 +5934,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5859,16 +5960,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -5876,7 +5977,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>20</v>
@@ -5918,7 +6019,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -5933,15 +6034,15 @@
         <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5964,13 +6065,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -5997,13 +6098,11 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -6021,7 +6120,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6033,34 +6132,34 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -6075,7 +6174,7 @@
         <v>30</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6146,10 +6245,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6249,10 +6348,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6352,10 +6451,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6378,16 +6477,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6395,7 +6494,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>20</v>
@@ -6437,7 +6536,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -6452,15 +6551,15 @@
         <v>20</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6483,13 +6582,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6516,13 +6615,11 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -6540,7 +6637,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6552,21 +6649,21 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>20</v>
@@ -6576,7 +6673,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -6594,7 +6691,7 @@
         <v>30</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6665,10 +6762,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6768,10 +6865,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6871,10 +6968,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6897,16 +6994,16 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -6914,7 +7011,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>20</v>
@@ -6956,7 +7053,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -6971,15 +7068,15 @@
         <v>20</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7002,13 +7099,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7059,7 +7156,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -7071,26 +7168,28 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>82</v>
@@ -7105,24 +7204,22 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>20</v>
@@ -7164,30 +7261,30 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>117</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7198,7 +7295,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -7210,13 +7307,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7267,7 +7364,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7279,14 +7376,2090 @@
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>109</v>
       </c>
+      <c r="AG68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK61">
+  <autoFilter ref="A1:AK81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7296,7 +9469,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
